--- a/data/distances.xlsx
+++ b/data/distances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b7551e2db3795b8/VS Code/OneDrive/GitHub/Sierre-District-Food-Drone-Delivery/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_2B59D2BFD3E0595D4BBA2D11591308F15F93E736" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1092B269-9B27-4B9E-AFEC-6DD0695AC593}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_2B59D2BFD3E0595D4BBA2D11591308F15F93E736" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA6519E8-8C21-4CBE-B912-F7B9B51ECF0C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
   <si>
     <t>Anniviers</t>
   </si>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -846,6 +846,44 @@
         <v>1.9902173678822399</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>12.81422213871878</v>
+      </c>
+      <c r="C12">
+        <v>1.8566459912241531</v>
+      </c>
+      <c r="D12">
+        <v>2.4207877655988059</v>
+      </c>
+      <c r="E12">
+        <v>4.0770722244529853</v>
+      </c>
+      <c r="F12">
+        <v>5.2407110345060914</v>
+      </c>
+      <c r="G12">
+        <v>5.7095752851229573</v>
+      </c>
+      <c r="H12">
+        <v>5.2313901319159788</v>
+      </c>
+      <c r="I12">
+        <v>4.3660015358378974</v>
+      </c>
+      <c r="J12">
+        <v>8.201150043788477</v>
+      </c>
+      <c r="K12">
+        <v>1.9902173678822399</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
